--- a/TESTDCF8_test7.xlsx
+++ b/TESTDCF8_test7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mydrive.metlife.com/personal/michael_steinberg_metlife_com/Documents/Desktop/stochasticmodel_sandbox/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f2d3817d0f7987d/Desktop/stochastic_model_sandbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{15C01B17-746E-4ABF-A7BF-674A9D12EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5119176B-2C15-4BB0-ABA6-BF30E63226F9}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{15C01B17-746E-4ABF-A7BF-674A9D12EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8111480D-4B61-471E-AE4B-6293C3761C5F}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F92A932-4862-4E03-8261-7584EC3D15AE}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{1F92A932-4862-4E03-8261-7584EC3D15AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="57">
   <si>
     <t>value</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>Sale</t>
+  </si>
+  <si>
+    <t>rev_exp_corr</t>
   </si>
 </sst>
 </file>
@@ -837,22 +840,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD3F3CE-8871-43BD-B6FC-D316A08E48F7}">
-  <dimension ref="A1:U50"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V50"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="19.7109375" style="16" customWidth="1"/>
-    <col min="12" max="13" width="8.7109375" style="15"/>
-    <col min="14" max="14" width="12.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="11" width="19.7265625" style="16" customWidth="1"/>
+    <col min="12" max="13" width="8.7265625" style="15"/>
+    <col min="14" max="14" width="12.1796875" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.7109375" style="15"/>
+    <col min="16" max="17" width="10.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.26953125" style="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.26953125" style="15" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.7265625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -916,8 +919,11 @@
       <c r="U1" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -985,8 +991,11 @@
       <c r="U2" s="6">
         <v>9.9375000000000005E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="15">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1054,8 +1063,11 @@
       <c r="U3" s="6">
         <v>9.2968749999999975E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1123,8 +1135,11 @@
       <c r="U4" s="6">
         <v>8.3026315789473684E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="15">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1192,8 +1207,11 @@
       <c r="U5" s="6">
         <v>0.10181818181818181</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" s="15">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1261,8 +1279,11 @@
       <c r="U6" s="6">
         <v>7.9166666666666677E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1330,8 +1351,11 @@
       <c r="U7" s="6">
         <v>7.2500000000000009E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V7" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>25</v>
       </c>
@@ -1399,8 +1423,11 @@
       <c r="U8" s="6">
         <v>7.9218749999999991E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" s="15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -1468,8 +1495,11 @@
       <c r="U9" s="6">
         <v>9.2142857142857151E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" s="15">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1537,8 +1567,11 @@
       <c r="U10" s="6">
         <v>8.9253090659340659E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1606,8 +1639,11 @@
       <c r="U11" s="6">
         <v>7.7343749999999975E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -1675,8 +1711,11 @@
       <c r="U12" s="6">
         <v>0.10006410256410257</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="15">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1744,8 +1783,11 @@
       <c r="U13" s="6">
         <v>7.3571428571428552E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="15">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1813,8 +1855,11 @@
       <c r="U14" s="6">
         <v>7.3881578947368423E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="15">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -1882,8 +1927,11 @@
       <c r="U15" s="6">
         <v>8.0520833333333333E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="15">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -1951,8 +1999,11 @@
       <c r="U16" s="6">
         <v>7.6875000000000013E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -2020,8 +2071,11 @@
       <c r="U17" s="6">
         <v>8.4062500000000026E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="15">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -2089,8 +2143,11 @@
       <c r="U18" s="5">
         <v>7.2499999999999995E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="15">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -2158,8 +2215,11 @@
       <c r="U19" s="6">
         <v>7.9596774193548395E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="15">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -2227,8 +2287,11 @@
       <c r="U20" s="6">
         <v>0.08</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" s="15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -2296,8 +2359,11 @@
       <c r="U21" s="6">
         <v>7.8557692307692342E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" s="15">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -2365,125 +2431,128 @@
       <c r="U22" s="6">
         <v>7.2708333333333333E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="15">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
       <c r="E24" s="19"/>
       <c r="G24" s="19"/>
       <c r="J24" s="19"/>
       <c r="L24" s="20"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
       <c r="J25" s="19"/>
       <c r="L25" s="21"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H28" s="17"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H29" s="17"/>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H30" s="17"/>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H31" s="17"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="H32" s="17"/>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H33" s="17"/>
       <c r="J33" s="18"/>
       <c r="K33" s="18"/>
     </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H34" s="17"/>
       <c r="J34" s="18"/>
       <c r="K34" s="18"/>
     </row>
-    <row r="35" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H35" s="17"/>
       <c r="J35" s="18"/>
       <c r="K35" s="18"/>
     </row>
-    <row r="36" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H36" s="17"/>
       <c r="J36" s="18"/>
       <c r="K36" s="18"/>
     </row>
-    <row r="37" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H37" s="17"/>
       <c r="J37" s="18"/>
       <c r="K37" s="18"/>
     </row>
-    <row r="38" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H38" s="17"/>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
     </row>
-    <row r="39" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H39" s="17"/>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
     </row>
-    <row r="40" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H40" s="17"/>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
     </row>
-    <row r="41" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H41" s="17"/>
       <c r="J41" s="18"/>
       <c r="K41" s="18"/>
     </row>
-    <row r="42" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H42" s="17"/>
       <c r="J42" s="18"/>
       <c r="K42" s="18"/>
     </row>
-    <row r="43" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H43" s="17"/>
       <c r="J43" s="18"/>
       <c r="K43" s="18"/>
     </row>
-    <row r="44" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H44" s="17"/>
       <c r="J44" s="18"/>
       <c r="K44" s="18"/>
     </row>
-    <row r="45" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H45" s="17"/>
       <c r="J45" s="18"/>
       <c r="K45" s="18"/>
     </row>
-    <row r="46" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H46" s="17"/>
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
     </row>
-    <row r="47" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H47" s="17"/>
       <c r="J47" s="18"/>
       <c r="K47" s="18"/>
     </row>
-    <row r="48" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="8:11" x14ac:dyDescent="0.35">
       <c r="H48" s="17"/>
       <c r="J48" s="18"/>
       <c r="K48" s="18"/>
     </row>
-    <row r="49" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J49" s="18"/>
       <c r="K49" s="18"/>
     </row>
-    <row r="50" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="10:11" x14ac:dyDescent="0.35">
       <c r="J50" s="18"/>
       <c r="K50" s="18"/>
     </row>
@@ -2495,28 +2564,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CF0DBB-EEAE-4857-81A2-7D3883DEB14F}">
   <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="7.54296875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="2" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7109375" style="1"/>
+    <col min="5" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1"/>
       <c r="C1" s="40" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C4" s="23" t="s">
         <v>49</v>
       </c>
@@ -2525,7 +2594,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C5" s="24" t="s">
         <v>50</v>
       </c>
@@ -2534,7 +2603,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C6" s="24" t="s">
         <v>43</v>
       </c>
@@ -2543,7 +2612,7 @@
         <v>0.23006214435337946</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C7" s="24" t="s">
         <v>45</v>
       </c>
@@ -2552,7 +2621,7 @@
         <v>5.8500000000000003E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="C8" s="24" t="s">
         <v>46</v>
       </c>
@@ -2561,7 +2630,7 @@
         <v>6.1500000000000006E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
@@ -2570,7 +2639,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2622,7 +2691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2672,7 +2741,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2694,7 +2763,7 @@
       <c r="N13" s="34"/>
       <c r="O13" s="34"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2747,7 +2816,7 @@
         <v>17.318858133544634</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2800,7 +2869,7 @@
         <v>7.8619108191631168</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -2853,7 +2922,7 @@
         <v>9.4569473143815159</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2906,7 +2975,7 @@
         <v>2.1756855781835447</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2959,7 +3028,7 @@
         <v>7.2812617361979708</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -2982,7 +3051,7 @@
       </c>
       <c r="O19" s="34"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -3035,7 +3104,7 @@
       </c>
       <c r="O20" s="34"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -3053,7 +3122,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>32</v>
       </c>
@@ -3076,7 +3145,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3099,7 +3168,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3116,27 +3185,27 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>39</v>
       </c>

--- a/TESTDCF8_test7.xlsx
+++ b/TESTDCF8_test7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f2d3817d0f7987d/Desktop/stochastic_model_sandbox/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{15C01B17-746E-4ABF-A7BF-674A9D12EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8111480D-4B61-471E-AE4B-6293C3761C5F}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{15C01B17-746E-4ABF-A7BF-674A9D12EB18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA5DC267-9BE8-4C7F-8450-E11C60C18ED0}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{1F92A932-4862-4E03-8261-7584EC3D15AE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{1F92A932-4862-4E03-8261-7584EC3D15AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -521,6 +521,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1535,7 +1539,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="K10" s="8">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L10" s="11">
         <v>0.10525647584898666</v>
@@ -1679,7 +1683,7 @@
         <v>0.11849999999999999</v>
       </c>
       <c r="K12" s="8">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L12" s="11">
         <v>9.5687705317260591E-2</v>
